--- a/output/fambox/FAMBOX_Flywheel_週次計画_2026-05-28.xlsx
+++ b/output/fambox/FAMBOX_Flywheel_週次計画_2026-05-28.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20" yWindow="600" windowWidth="28800" windowHeight="17400" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_概要" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,25 +19,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="48">
+  <fonts count="44">
     <font>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Yu Gothic UI"/>
-      <b val="1"/>
-      <color rgb="FF1B1D1A"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK JP"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF1B1D1A"/>
-      <sz val="18"/>
     </font>
     <font>
       <name val="Noto Sans CJK JP"/>
@@ -48,35 +35,9 @@
     </font>
     <font>
       <name val="Yu Gothic UI"/>
-      <i val="1"/>
-      <color rgb="FF545655"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK JP"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF1B1D1A"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK JP"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FF1B1D1A"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Yu Gothic UI"/>
-      <b val="1"/>
-      <color rgb="FF1B1D1A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK JP"/>
-      <family val="2"/>
-      <color rgb="FF545655"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Noto Sans CJK JP"/>
@@ -112,12 +73,6 @@
     <font>
       <name val="Yu Gothic UI"/>
       <b val="1"/>
-      <color rgb="FF1B1D1A"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Yu Gothic UI"/>
-      <b val="1"/>
       <color rgb="FFFB4C15"/>
       <sz val="10"/>
     </font>
@@ -143,12 +98,6 @@
     <font>
       <name val="Yu Gothic UI"/>
       <b val="1"/>
-      <color rgb="FF1B1D1A"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Yu Gothic UI"/>
-      <b val="1"/>
       <color rgb="FFFB4C15"/>
       <sz val="12"/>
     </font>
@@ -177,13 +126,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Noto Sans CJK JP"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0F2A5C"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Yu Gothic UI"/>
       <b val="1"/>
       <color rgb="FF3DB8E8"/>
@@ -238,42 +180,87 @@
     <font>
       <name val="Yu Gothic UI"/>
       <b val="1"/>
-      <color rgb="001B1D1A"/>
+      <color rgb="FF1B1D1A"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Yu Gothic UI"/>
       <i val="1"/>
-      <color rgb="00545655"/>
+      <color rgb="FF545655"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Yu Gothic UI"/>
       <b val="1"/>
-      <color rgb="001B1D1A"/>
+      <color rgb="FF1B1D1A"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Yu Gothic UI"/>
       <b val="1"/>
-      <color rgb="001B1D1A"/>
+      <color rgb="FF1B1D1A"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Yu Gothic UI"/>
-      <color rgb="00545655"/>
+      <color rgb="FF545655"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Yu Gothic UI"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <color rgb="FF1B1D1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <b val="1"/>
+      <color rgb="FF1B1D1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <b val="1"/>
+      <color rgb="FFFB4C15"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <b val="1"/>
+      <color rgb="FFFB4C15"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <b val="1"/>
+      <color rgb="FF1B1D1A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <b val="1"/>
+      <color rgb="FF0F2A5C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <color rgb="FF1B1D1A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic UI"/>
+      <color rgb="FF545655"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Yu Gothic UI"/>
       <color rgb="001B1D1A"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Yu Gothic UI"/>
@@ -284,39 +271,22 @@
     <font>
       <name val="Yu Gothic UI"/>
       <b val="1"/>
-      <color rgb="00FB4C15"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Yu Gothic UI"/>
       <b val="1"/>
       <color rgb="00FB4C15"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Yu Gothic UI"/>
-      <b val="1"/>
-      <color rgb="001B1D1A"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Yu Gothic UI"/>
-      <b val="1"/>
-      <color rgb="000F2A5C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Yu Gothic UI"/>
       <color rgb="001B1D1A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Yu Gothic UI"/>
-      <color rgb="00545655"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -327,12 +297,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFB4C15"/>
         <bgColor rgb="FFFF8080"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF4E5"/>
-        <bgColor rgb="FFFAFAFA"/>
       </patternFill>
     </fill>
     <fill>
@@ -367,26 +331,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FB4C15"/>
+        <fgColor rgb="FFFB4C15"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF4E5"/>
+        <fgColor rgb="FFFFF4E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -410,23 +384,18 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      <left style="thin">
         <color rgb="FFECECEC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      </left>
       <right style="thin">
         <color rgb="FFECECEC"/>
       </right>
       <top style="thin">
         <color rgb="FFECECEC"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFECECEC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -455,6 +424,85 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFFB4C15"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFB4C15"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFB4C15"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFB4C15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFB4C15"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFB4C15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFB4C15"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFB4C15"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFB4C15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFECECEC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFECECEC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFECECEC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFB4C15"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFB4C15"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFB4C15"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="00ECECEC"/>
       </left>
       <right style="thin">
@@ -467,317 +515,228 @@
         <color rgb="00ECECEC"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00ECECEC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00ECECEC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00ECECEC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00ECECEC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00ECECEC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00ECECEC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00ECECEC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00ECECEC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00FB4C15"/>
-      </left>
-      <right style="thin">
-        <color rgb="00FB4C15"/>
-      </right>
-      <top style="thin">
-        <color rgb="00FB4C15"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00FB4C15"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00FB4C15"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00FB4C15"/>
-      </right>
-      <top style="thin">
-        <color rgb="00FB4C15"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00FB4C15"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00FB4C15"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00FB4C15"/>
-      </right>
-      <top style="thin">
-        <color rgb="00FB4C15"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00FB4C15"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1041,397 +1000,396 @@
   <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.83203125" defaultRowHeight="20"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="6"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" style="54" min="1" max="1"/>
+    <col width="30" customWidth="1" style="54" min="2" max="2"/>
+    <col width="22" customWidth="1" style="54" min="3" max="3"/>
+    <col width="32" customWidth="1" style="54" min="4" max="4"/>
+    <col width="20" customWidth="1" style="54" min="5" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="54">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>FAMBOX Design Flywheel — 週次宣言計画表</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="57" t="inlineStr">
         <is>
           <t>作成：宮川真道 / 2026-05-28 / Step 1（個人インフラ構築）</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="53" t="inlineStr">
+    <row r="4" ht="22" customHeight="1" s="54">
+      <c r="A4" s="56" t="inlineStr">
         <is>
           <t>🎯 目的</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="54" t="inlineStr">
+    <row r="5" ht="25" customHeight="1" s="54">
+      <c r="A5" s="66" t="inlineStr">
         <is>
           <t>誰でも 7割の質のアウトプットを早く出せる、AI と Design の仕組み(インフラ)を作る</t>
         </is>
       </c>
-      <c r="B5" s="55" t="n"/>
-      <c r="C5" s="55" t="n"/>
-      <c r="D5" s="55" t="n"/>
-      <c r="E5" s="55" t="n"/>
-      <c r="F5" s="56" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="57" t="inlineStr">
+      <c r="B5" s="62" t="n"/>
+      <c r="C5" s="62" t="n"/>
+      <c r="D5" s="62" t="n"/>
+      <c r="E5" s="62" t="n"/>
+      <c r="F5" s="63" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="54">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>迷いを断ち、緊張感を持って毎週前進。須藤さん助言「公共宣言で逃げ場を断つ」を実装。</t>
         </is>
       </c>
-      <c r="B6" s="55" t="n"/>
-      <c r="C6" s="55" t="n"/>
-      <c r="D6" s="55" t="n"/>
-      <c r="E6" s="55" t="n"/>
-      <c r="F6" s="56" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="53" t="inlineStr">
+      <c r="B6" s="62" t="n"/>
+      <c r="C6" s="62" t="n"/>
+      <c r="D6" s="62" t="n"/>
+      <c r="E6" s="62" t="n"/>
+      <c r="F6" s="63" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="54">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>🔁 運用サイクル</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="58" t="inlineStr">
+    <row r="9" ht="21" customHeight="1" s="54">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="B9" s="58" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>アクション</t>
         </is>
       </c>
-      <c r="C9" s="58" t="inlineStr">
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t>場所</t>
         </is>
       </c>
-      <c r="D9" s="58" t="inlineStr">
+      <c r="D9" s="43" t="inlineStr">
         <is>
           <t>目的</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>月曜 9:00-10:00</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>宣言 + 先週の成果を投稿</t>
         </is>
       </c>
-      <c r="C10" s="60" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>#int-general</t>
         </is>
       </c>
-      <c r="D10" s="60" t="inlineStr">
+      <c r="D10" s="61" t="inlineStr">
         <is>
           <t>公共宣言で逃げ場を断つ</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t>火 - 木</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>実行（緊張感を持って）</t>
         </is>
       </c>
-      <c r="C11" s="60" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>実作業</t>
         </is>
       </c>
-      <c r="D11" s="60" t="inlineStr">
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>宣言した3つを達成</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="44" t="inlineStr">
         <is>
           <t>水曜 夕方</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>中間チェック → 必要なら Update 投稿</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="61" t="inlineStr">
         <is>
           <t>#int-general</t>
         </is>
       </c>
-      <c r="D12" s="60" t="inlineStr">
+      <c r="D12" s="61" t="inlineStr">
         <is>
           <t>詰まりを早期検知 + 軌道修正</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="59" t="inlineStr">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>金曜 17:00</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>進捗報告</t>
         </is>
       </c>
-      <c r="C13" s="60" t="inlineStr">
+      <c r="C13" s="61" t="inlineStr">
         <is>
           <t>事業開発</t>
         </is>
       </c>
-      <c r="D13" s="60" t="inlineStr">
+      <c r="D13" s="61" t="inlineStr">
         <is>
           <t>週次レビュー(Marc/須藤同席)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="59" t="inlineStr">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>土・日</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t>Retro + 次週ドラフト</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="61" t="inlineStr">
         <is>
           <t>個人作業</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr">
+      <c r="D14" s="61" t="inlineStr">
         <is>
           <t>次週の宣言を仮置き</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="53" t="inlineStr">
+    <row r="16" ht="22" customHeight="1" s="54"/>
+    <row r="17" ht="21" customHeight="1" s="54">
+      <c r="A17" s="56" t="inlineStr">
         <is>
           <t>📝 月曜投稿フォーマット（#int-general）</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="57" customHeight="1">
-      <c r="A18" s="58" t="inlineStr"/>
-      <c r="B18" s="58" t="inlineStr">
+    <row r="18" ht="57" customHeight="1" s="54">
+      <c r="A18" s="43" t="n"/>
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>セクション</t>
         </is>
       </c>
-      <c r="C18" s="58" t="inlineStr">
+      <c r="C18" s="43" t="inlineStr">
         <is>
           <t>中身</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="57" customHeight="1">
-      <c r="A19" s="61" t="inlineStr">
+    <row r="19" ht="57" customHeight="1" s="54">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>Part 1</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>✅ 先週やったこと</t>
         </is>
       </c>
-      <c r="C19" s="60" t="inlineStr">
+      <c r="C19" s="61" t="inlineStr">
         <is>
           <t>成果物リスト + 学び1行 + 倒れた項目(あれば理由+対策)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="61" t="inlineStr">
+    <row r="20" ht="38" customHeight="1" s="54">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>Part 2</t>
         </is>
       </c>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>🎯 今週の宣言</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
+      <c r="C20" s="61" t="inlineStr">
         <is>
           <t>最大3つ、各項目に [動詞 + 具体物 + 期限] を含める</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="61" t="inlineStr">
+      <c r="A21" s="46" t="inlineStr">
         <is>
           <t>Part 3</t>
         </is>
       </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>📈 Flywheel 進捗</t>
         </is>
       </c>
-      <c r="C21" s="60" t="inlineStr">
+      <c r="C21" s="61" t="inlineStr">
         <is>
           <t>現在の Step + 次マイルストーン</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1"/>
-    <row r="24" ht="39.75" customHeight="1">
-      <c r="A24" s="53" t="inlineStr">
+    <row r="23" ht="22" customHeight="1" s="54"/>
+    <row r="24" ht="39.75" customHeight="1" s="54">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t>🔧 途中修正ルール（週の途中で宣言を変えたい時）</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="57" t="inlineStr">
+    <row r="25" ht="30" customHeight="1" s="54">
+      <c r="A25" s="67" t="inlineStr">
         <is>
           <t>宣言通り進まない時、迷ったり罪悪感を感じない仕組み。下記4ルールに従えば「修正＝悪」ではなく「健全な軌道修正」になる。</t>
         </is>
       </c>
-      <c r="B25" s="55" t="n"/>
-      <c r="C25" s="55" t="n"/>
-      <c r="D25" s="55" t="n"/>
-      <c r="E25" s="55" t="n"/>
-      <c r="F25" s="56" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="58" t="inlineStr">
+      <c r="B25" s="62" t="n"/>
+      <c r="C25" s="62" t="n"/>
+      <c r="D25" s="62" t="n"/>
+      <c r="E25" s="62" t="n"/>
+      <c r="F25" s="63" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" s="54">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>Rule</t>
         </is>
       </c>
-      <c r="B26" s="58" t="inlineStr">
+      <c r="B26" s="43" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C26" s="58" t="inlineStr">
+      <c r="C26" s="43" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="62" t="inlineStr">
+    <row r="27" ht="28" customHeight="1" s="54">
+      <c r="A27" s="47" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B27" s="59" t="inlineStr">
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>3宣言の上限は絶対に守る。増やすなら必ず1つ削る</t>
         </is>
       </c>
-      <c r="C27" s="60" t="inlineStr">
+      <c r="C27" s="61" t="inlineStr">
         <is>
           <t>4つ以上はパンクの予兆（須藤さん助言の核心）</t>
         </is>
       </c>
-      <c r="D27" s="55" t="n"/>
-      <c r="E27" s="55" t="n"/>
-      <c r="F27" s="56" t="n"/>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="62" t="inlineStr">
+      <c r="D27" s="62" t="n"/>
+      <c r="E27" s="62" t="n"/>
+      <c r="F27" s="63" t="n"/>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="54">
+      <c r="A28" s="47" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="59" t="inlineStr">
+      <c r="B28" s="44" t="inlineStr">
         <is>
           <t>スコープ変更は「縮める」のみ OK、「広げる」は NG</t>
         </is>
       </c>
-      <c r="C28" s="60" t="inlineStr">
+      <c r="C28" s="61" t="inlineStr">
         <is>
           <t>「縮める」は品質 7 と整合。「広げる」は破綻のもと</t>
         </is>
       </c>
-      <c r="D28" s="55" t="n"/>
-      <c r="E28" s="55" t="n"/>
-      <c r="F28" s="56" t="n"/>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="62" t="inlineStr">
+      <c r="D28" s="62" t="n"/>
+      <c r="E28" s="62" t="n"/>
+      <c r="F28" s="63" t="n"/>
+    </row>
+    <row r="29" ht="28" customHeight="1" s="54">
+      <c r="A29" s="47" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B29" s="59" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>修正は必ず公開する：Slack に「🛞 Update: 宣言○を△に差し替え」</t>
         </is>
       </c>
-      <c r="C29" s="60" t="inlineStr">
+      <c r="C29" s="61" t="inlineStr">
         <is>
           <t>逃げ場が消える効果を継続させる</t>
         </is>
       </c>
-      <c r="D29" s="55" t="n"/>
-      <c r="E29" s="55" t="n"/>
-      <c r="F29" s="56" t="n"/>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="62" t="inlineStr">
+      <c r="D29" s="62" t="n"/>
+      <c r="E29" s="62" t="n"/>
+      <c r="F29" s="63" t="n"/>
+    </row>
+    <row r="30" ht="28" customHeight="1" s="54">
+      <c r="A30" s="47" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B30" s="59" t="inlineStr">
+      <c r="B30" s="44" t="inlineStr">
         <is>
           <t>ドロップしたら必ず代替宣言を立てる。「無宣言週」を作らない</t>
         </is>
       </c>
-      <c r="C30" s="60" t="inlineStr">
+      <c r="C30" s="61" t="inlineStr">
         <is>
           <t>倒れた時こそ Learn 機会、空欄は学習停止のサイン</t>
         </is>
       </c>
-      <c r="D30" s="55" t="n"/>
-      <c r="E30" s="55" t="n"/>
-      <c r="F30" s="56" t="n"/>
-    </row>
-    <row r="31" ht="38" customHeight="1"/>
+      <c r="D30" s="62" t="n"/>
+      <c r="E30" s="62" t="n"/>
+      <c r="F30" s="63" t="n"/>
+    </row>
+    <row r="31" ht="38" customHeight="1" s="54"/>
     <row r="32">
-      <c r="A32" s="63" t="inlineStr">
+      <c r="A32" s="48" t="inlineStr">
         <is>
           <t>📋 動的調整フロー（実運用）</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="130" customHeight="1">
-      <c r="A33" s="64" t="inlineStr">
+    <row r="33" ht="130" customHeight="1" s="54">
+      <c r="A33" s="58" t="inlineStr">
         <is>
           <t>月曜 9-10時  →  宣言投稿(3項目)
 火・水       →  実行
@@ -1443,204 +1401,204 @@
 週末         →  retro + 次週ドラフト</t>
         </is>
       </c>
-      <c r="B33" s="65" t="n"/>
-      <c r="C33" s="65" t="n"/>
-      <c r="D33" s="65" t="n"/>
-      <c r="E33" s="65" t="n"/>
-      <c r="F33" s="66" t="n"/>
+      <c r="B33" s="59" t="n"/>
+      <c r="C33" s="59" t="n"/>
+      <c r="D33" s="59" t="n"/>
+      <c r="E33" s="59" t="n"/>
+      <c r="F33" s="60" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="63" t="inlineStr">
+      <c r="A35" s="48" t="inlineStr">
         <is>
           <t>💡 新しいアイデアが浮かんだら</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="58" t="inlineStr">
+      <c r="A36" s="43" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="B36" s="58" t="inlineStr">
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>行き先</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="67" t="inlineStr">
+      <c r="A37" s="49" t="inlineStr">
         <is>
           <t>今週やりたい</t>
         </is>
       </c>
-      <c r="B37" s="60" t="inlineStr">
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>既存3宣言の1つと差し替え（Rule 1 適用）</t>
         </is>
       </c>
-      <c r="C37" s="55" t="n"/>
-      <c r="D37" s="55" t="n"/>
-      <c r="E37" s="55" t="n"/>
-      <c r="F37" s="56" t="n"/>
+      <c r="C37" s="62" t="n"/>
+      <c r="D37" s="62" t="n"/>
+      <c r="E37" s="62" t="n"/>
+      <c r="F37" s="63" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="67" t="inlineStr">
+      <c r="A38" s="49" t="inlineStr">
         <is>
           <t>将来やりたい</t>
         </is>
       </c>
-      <c r="B38" s="60" t="inlineStr">
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>Sheet 3「テーマプール」に追加 → 来週以降の候補に</t>
         </is>
       </c>
-      <c r="C38" s="55" t="n"/>
-      <c r="D38" s="55" t="n"/>
-      <c r="E38" s="55" t="n"/>
-      <c r="F38" s="56" t="n"/>
+      <c r="C38" s="62" t="n"/>
+      <c r="D38" s="62" t="n"/>
+      <c r="E38" s="62" t="n"/>
+      <c r="F38" s="63" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="67" t="inlineStr">
+      <c r="A39" s="49" t="inlineStr">
         <is>
           <t>構造的決定</t>
         </is>
       </c>
-      <c r="B39" s="60" t="inlineStr">
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t>DECISIONS.md に D-NNN として追加</t>
         </is>
       </c>
-      <c r="C39" s="55" t="n"/>
-      <c r="D39" s="55" t="n"/>
-      <c r="E39" s="55" t="n"/>
-      <c r="F39" s="56" t="n"/>
+      <c r="C39" s="62" t="n"/>
+      <c r="D39" s="62" t="n"/>
+      <c r="E39" s="62" t="n"/>
+      <c r="F39" s="63" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="53" t="inlineStr">
+      <c r="A42" s="56" t="inlineStr">
         <is>
           <t>🚨 緊急ルール（破綻防止）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="40" customHeight="1">
+    <row r="43" ht="40" customHeight="1" s="54">
       <c r="A43" s="68" t="inlineStr">
         <is>
           <t>3週連続で宣言の半分以上が倒れたら、Marc or 須藤と 1on1 で立て直し。構造的問題か / 優先業務侵食か / モチベーション低下か を切り分け。</t>
         </is>
       </c>
-      <c r="B43" s="55" t="n"/>
-      <c r="C43" s="55" t="n"/>
-      <c r="D43" s="55" t="n"/>
-      <c r="E43" s="55" t="n"/>
-      <c r="F43" s="56" t="n"/>
+      <c r="B43" s="62" t="n"/>
+      <c r="C43" s="62" t="n"/>
+      <c r="D43" s="62" t="n"/>
+      <c r="E43" s="62" t="n"/>
+      <c r="F43" s="63" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="53" t="inlineStr">
+      <c r="A45" s="56" t="inlineStr">
         <is>
           <t>💾 Claude セッション継続方法</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="50" customHeight="1">
-      <c r="A46" s="69" t="inlineStr">
+    <row r="46" ht="50" customHeight="1" s="54">
+      <c r="A46" s="64" t="inlineStr">
         <is>
           <t>新しい Claude セッションで「Flywheel の続き」と書くだけ。私が MEMORY.md → project_fambox_flywheel.md を自動で読み、PROGRESS.md と直近 session log から完全復元する。全 commit が GitHub に push 済なので、データロス 0。</t>
         </is>
       </c>
-      <c r="B46" s="55" t="n"/>
-      <c r="C46" s="55" t="n"/>
-      <c r="D46" s="55" t="n"/>
-      <c r="E46" s="55" t="n"/>
-      <c r="F46" s="56" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="63" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="53" t="inlineStr">
+      <c r="A48" s="56" t="inlineStr">
         <is>
           <t>🔗 関連意思決定（DECISIONS.md）</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="58" t="inlineStr">
+      <c r="A49" s="43" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B49" s="58" t="inlineStr">
+      <c r="B49" s="43" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C49" s="58" t="inlineStr">
+      <c r="C49" s="43" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="67" t="inlineStr">
+      <c r="A50" s="49" t="inlineStr">
         <is>
           <t>D-026</t>
         </is>
       </c>
-      <c r="B50" s="60" t="inlineStr">
+      <c r="B50" s="61" t="inlineStr">
         <is>
           <t>宣言駆動 Weekly Cycle 採用</t>
         </is>
       </c>
-      <c r="C50" s="60" t="inlineStr">
+      <c r="C50" s="61" t="inlineStr">
         <is>
           <t>毎週月曜 #int-general 投稿</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="67" t="inlineStr">
+    <row r="51" ht="30" customHeight="1" s="54">
+      <c r="A51" s="49" t="inlineStr">
         <is>
           <t>D-027</t>
         </is>
       </c>
-      <c r="B51" s="60" t="inlineStr">
+      <c r="B51" s="61" t="inlineStr">
         <is>
           <t>「スピード 10 / 品質 7」プロジェクト</t>
         </is>
       </c>
-      <c r="C51" s="60" t="inlineStr">
+      <c r="C51" s="61" t="inlineStr">
         <is>
           <t>完璧主義禁止、ゲーミフィケーション</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="67" t="inlineStr">
+    <row r="52" ht="30" customHeight="1" s="54">
+      <c r="A52" s="49" t="inlineStr">
         <is>
           <t>D-028</t>
         </is>
       </c>
-      <c r="B52" s="60" t="inlineStr">
+      <c r="B52" s="61" t="inlineStr">
         <is>
           <t>AI 自動化フロンティアを紙媒体・バナーに拡張</t>
         </is>
       </c>
-      <c r="C52" s="60" t="inlineStr">
+      <c r="C52" s="61" t="inlineStr">
         <is>
           <t>Web/Liquid 以外へ</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="67" t="inlineStr">
+      <c r="A53" s="49" t="inlineStr">
         <is>
           <t>D-029</t>
         </is>
       </c>
-      <c r="B53" s="60" t="inlineStr">
+      <c r="B53" s="61" t="inlineStr">
         <is>
           <t>6/24 千葉工大講演をパンケ活動化</t>
         </is>
       </c>
-      <c r="C53" s="60" t="inlineStr">
+      <c r="C53" s="61" t="inlineStr">
         <is>
           <t>対外発信</t>
         </is>
@@ -1676,1085 +1634,1135 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.83203125" defaultRowHeight="20"/>
   <cols>
-    <col width="7.33203125" customWidth="1" min="1" max="1"/>
-    <col width="11.83203125" customWidth="1" min="2" max="2"/>
-    <col width="12.6640625" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="31.83203125" customWidth="1" min="5" max="7"/>
-    <col width="7.33203125" customWidth="1" min="8" max="10"/>
-    <col width="22.6640625" customWidth="1" min="11" max="12"/>
+    <col width="7.33203125" customWidth="1" style="54" min="1" max="1"/>
+    <col width="11.83203125" customWidth="1" style="54" min="2" max="2"/>
+    <col width="12.6640625" customWidth="1" style="54" min="3" max="3"/>
+    <col width="20" customWidth="1" style="54" min="4" max="4"/>
+    <col width="31.83203125" customWidth="1" style="54" min="5" max="7"/>
+    <col width="7.33203125" customWidth="1" style="54" min="8" max="10"/>
+    <col width="22.6640625" customWidth="1" style="54" min="11" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="23" customHeight="1" s="54">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>週次ロードマップ — Week 2 〜 20（Step 1 → Step 2 → Step 3 移行）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>★ 各週、月曜に #int-general へ宣言投稿 / 金曜事業開発で進捗報告</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+    <row r="4" ht="31.5" customHeight="1" s="54">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Week #</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>投稿日 (月)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>テーマ</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>宣言1</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>宣言2</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>宣言3</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>達成1</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>達成2</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>達成3</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>学び</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>次週引継ぎ</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="69.75" customHeight="1">
-      <c r="A5" s="15" t="n">
+    <row r="5" ht="69.75" customHeight="1" s="54">
+      <c r="A5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Step 1</t>
         </is>
       </c>
-      <c r="D5" s="70" t="inlineStr">
+      <c r="D5" s="50" t="inlineStr">
         <is>
           <t>千葉工大講演準備 + 実案件着手</t>
         </is>
       </c>
-      <c r="E5" s="71" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>千葉工大講演スライド v0.1 作成（FAMBOX ブランド PPTX 自動化フローを試運用）— 木曜まで</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>法人ページ 1セクションを AI パイプラインで制作、Before/After 制作時間ログ取得（木）</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>紙 OR バナーの AI 自動化 1件試作（金）</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K5" s="19" t="n"/>
-      <c r="L5" s="72" t="inlineStr">
+      <c r="G5" s="70" t="inlineStr">
+        <is>
+          <t>第一弾プロジェクト：梱包用チラシ A4 を1タイプ試作（C向け OR B向け / Figma）、4ステップループ ①インプット→②生成→③レビュー修正→④学び の1サイクル目 — 金曜まで</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="52" t="inlineStr">
         <is>
           <t>※ Marc Archeco repo 招待 = 受動タスク。届いたら都度対応（宣言外）</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="69.75" customHeight="1">
-      <c r="A6" s="22" t="n">
+    <row r="6" ht="69.75" customHeight="1" s="54">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Step 1</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>バナー AI 自動化</t>
-        </is>
-      </c>
-      <c r="E6" s="25" t="inlineStr">
-        <is>
-          <t>バナー AI 自動化フロー完成 — 5案/週ペース可能に</t>
-        </is>
-      </c>
-      <c r="F6" s="25" t="inlineStr">
-        <is>
-          <t>指示書インプットフォーマット v1 作成（Standard 形式 Slack 化）</t>
-        </is>
-      </c>
-      <c r="G6" s="25" t="inlineStr">
-        <is>
-          <t>法人ページ 2セクション目を AI で制作</t>
-        </is>
-      </c>
-      <c r="H6" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I6" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J6" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K6" s="25" t="n"/>
-      <c r="L6" s="25" t="n"/>
-    </row>
-    <row r="7" ht="69.75" customHeight="1">
-      <c r="A7" s="15" t="n">
+      <c r="D6" s="71" t="inlineStr">
+        <is>
+          <t>梱包用チラシ 2タイプ目 + フロー安定化</t>
+        </is>
+      </c>
+      <c r="E6" s="72" t="inlineStr">
+        <is>
+          <t>チラシ 2タイプ目（C向け or B向け、Week 2 と逆）試作完成</t>
+        </is>
+      </c>
+      <c r="F6" s="72" t="inlineStr">
+        <is>
+          <t>指示書インプットフォーマット v1 をチラシ用に最適化</t>
+        </is>
+      </c>
+      <c r="G6" s="72" t="inlineStr">
+        <is>
+          <t>4ステップループ 2サイクル目を回す、学びを bugs.md に蓄積</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="69.75" customHeight="1" s="54">
+      <c r="A7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Step 1</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>お問い合わせ + チラシ</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>お問い合わせページを AI で再構築 — 7割品質</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>チラシ A4 自動化フロー試作</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>過去失敗 5件を bugs.md に追加（Marc M2 原則）</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K7" s="19" t="n"/>
-      <c r="L7" s="19" t="n"/>
-    </row>
-    <row r="8" ht="69.75" customHeight="1">
-      <c r="A8" s="22" t="n">
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="69.75" customHeight="1" s="54">
+      <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Step 1</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>千葉工大講演 + パンケ活動</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>6/24 千葉工大講演スライド作成（FAMBOX ブランド適用）</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>講演実施 + 録画共有（対外発信）</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>松浦さんに共有 → パンケ活動コンテンツ化</t>
         </is>
       </c>
-      <c r="H8" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I8" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J8" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K8" s="28" t="n"/>
-      <c r="L8" s="28" t="n"/>
-    </row>
-    <row r="9" ht="69.75" customHeight="1">
-      <c r="A9" s="15" t="n">
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K8" s="19" t="n"/>
+      <c r="L8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="69.75" customHeight="1" s="54">
+      <c r="A9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Step 1</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>紙媒体 AI フロー完成</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>チラシ/パンフ AI フロー完成（7割品質）</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>バナー量産テスト 10件</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>A→B 改良で何% 精度向上か計測（Learn 定量化）</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K9" s="19" t="n"/>
-      <c r="L9" s="19" t="n"/>
-    </row>
-    <row r="10" ht="69.75" customHeight="1">
-      <c r="A10" s="22" t="n">
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="69.75" customHeight="1" s="54">
+      <c r="A10" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Step 1</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>メール HTML AI</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>メール HTML AI 自動化（件名+本文 7割品質）</t>
         </is>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>Klaviyo / Seal 連携テスト 1本</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>金曜事業開発で 7月の状況総括</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I10" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J10" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K10" s="28" t="n"/>
-      <c r="L10" s="28" t="n"/>
-    </row>
-    <row r="11" ht="69.75" customHeight="1">
-      <c r="A11" s="15" t="n">
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="69.75" customHeight="1" s="54">
+      <c r="A11" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Step 1</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>デザインパターン拡張</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>新パターン 3つ学習 → DS v0.6 案</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>法人 LP 全体改修着手</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Marc レビュー会留学（1回参加）</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I11" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K11" s="19" t="n"/>
-      <c r="L11" s="19" t="n"/>
-    </row>
-    <row r="12" ht="69.75" customHeight="1">
-      <c r="A12" s="22" t="n">
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="69.75" customHeight="1" s="54">
+      <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Step 1 完成判定</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>Step 1 retro + Step 2 準備</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>10倍速の証拠を集める（Before/After データ整理）</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>bugs.md 整理 + DOCTRINE 抽出</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>Step 1 完成判定 + Step 2 計画提示</t>
         </is>
       </c>
-      <c r="H12" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I12" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J12" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K12" s="28" t="n"/>
-      <c r="L12" s="28" t="n"/>
-    </row>
-    <row r="13" ht="69.75" customHeight="1">
-      <c r="A13" s="15" t="n">
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="19" t="n"/>
+    </row>
+    <row r="13" ht="69.75" customHeight="1" s="54">
+      <c r="A13" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Step 1→2 移行</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>指示書テンプレ実運用試行</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>須藤さんから初回依頼を Slack 受信</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>指示書テンプレ v1 → v1.1 実運用</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Marc 中間共有 + 評価獲得</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K13" s="19" t="n"/>
-      <c r="L13" s="19" t="n"/>
-    </row>
-    <row r="14" ht="69.75" customHeight="1">
-      <c r="A14" s="22" t="n">
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="69.75" customHeight="1" s="54">
+      <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C14" s="30" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>Step 2 開始</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>共有インフラ運用立ち上げ</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>松浦さんから初回依頼を消化（2時間以内）</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>プロセス文書化（次回再現可能に）</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>brand/fambox/CLAUDE.md v1.0 確定</t>
         </is>
       </c>
-      <c r="H14" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I14" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J14" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K14" s="28" t="n"/>
-      <c r="L14" s="28" t="n"/>
-    </row>
-    <row r="15" ht="69.75" customHeight="1">
-      <c r="A15" s="15" t="n">
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="69.75" customHeight="1" s="54">
+      <c r="A15" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Step 2</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>依頼 3件回す</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>依頼 3件を消化（平均納品時間計測）</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>ボトルネック特定 + 改善</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>bugs.md 拡張（Step 2 固有の罠）</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K15" s="19" t="n"/>
-      <c r="L15" s="19" t="n"/>
-    </row>
-    <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="22" t="n">
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="69.75" customHeight="1" s="54">
+      <c r="A16" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>Step 2</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>お盆期間 軽め</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>軽めの試作 1件</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>retro + 改善</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr">
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>9月計画提示</t>
         </is>
       </c>
-      <c r="H16" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I16" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J16" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K16" s="28" t="n"/>
-      <c r="L16" s="28" t="n"/>
-    </row>
-    <row r="17" ht="69.75" customHeight="1">
-      <c r="A17" s="15" t="n">
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="n"/>
+      <c r="L16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="69.75" customHeight="1" s="54">
+      <c r="A17" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Step 2</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>依頼 5件チャレンジ</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>依頼 5件を消化</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>品質バラつき検証 + 標準化</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>bugs.md DOCTRINE 50件到達</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J17" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K17" s="19" t="n"/>
-      <c r="L17" s="19" t="n"/>
-    </row>
-    <row r="18" ht="69.75" customHeight="1">
-      <c r="A18" s="22" t="n">
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="69.75" customHeight="1" s="54">
+      <c r="A18" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>Step 2</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>マレル接続準備</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>マレルチーム研修プラン作成</t>
         </is>
       </c>
-      <c r="F18" s="25" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>サンプル渡し依頼（山本さんに先行）</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>Step 2 完成判定 進捗確認</t>
         </is>
       </c>
-      <c r="H18" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J18" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K18" s="28" t="n"/>
-      <c r="L18" s="28" t="n"/>
-    </row>
-    <row r="19" ht="69.75" customHeight="1">
-      <c r="A19" s="15" t="n">
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="69.75" customHeight="1" s="54">
+      <c r="A19" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>Step 2</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>SNS 画像自動化</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Instagram 投稿画像 5案/週 自動化</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>マレル 1名にパイロット</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>修正点ログ収集</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J19" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K19" s="19" t="n"/>
-      <c r="L19" s="19" t="n"/>
-    </row>
-    <row r="20" ht="69.75" customHeight="1">
-      <c r="A20" s="22" t="n">
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="69.75" customHeight="1" s="54">
+      <c r="A20" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C20" s="30" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>Step 2</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>パイロット拡張</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>マレル 2名目に展開</t>
         </is>
       </c>
-      <c r="F20" s="25" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>フィードバック収集 + 改善</t>
         </is>
       </c>
-      <c r="G20" s="25" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>ブランド逸脱自動検知 試作</t>
         </is>
       </c>
-      <c r="H20" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I20" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K20" s="28" t="n"/>
-      <c r="L20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="69.75" customHeight="1">
-      <c r="A21" s="15" t="n">
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="69.75" customHeight="1" s="54">
+      <c r="A21" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>Step 2→3 移行</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Step 3 準備</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Step 2 完成判定</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>retro + Step 3 計画提示</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Marc 中間共有 + フィードバック</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J21" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K21" s="19" t="n"/>
-      <c r="L21" s="19" t="n"/>
-    </row>
-    <row r="22" ht="69.75" customHeight="1">
-      <c r="A22" s="22" t="n">
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="69.75" customHeight="1" s="54">
+      <c r="A22" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>Step 3 開始</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>自走化試験</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>マレル 1名が独立投稿成功</t>
         </is>
       </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>エラー検知率測定</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>bugs.md 自動化検討</t>
         </is>
       </c>
-      <c r="H22" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I22" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J22" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K22" s="28" t="n"/>
-      <c r="L22" s="28" t="n"/>
-    </row>
-    <row r="23" ht="69.75" customHeight="1">
-      <c r="A23" s="15" t="n">
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="69.75" customHeight="1" s="54">
+      <c r="A23" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C23" s="33" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>Step 3</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>スケーリング</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>マレル全員に展開</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>自走率 30% 目標</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Q4 計画 + Flywheel MVP ロードマップ</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J23" s="21" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="K23" s="19" t="n"/>
-      <c r="L23" s="19" t="n"/>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="69.75" customHeight="1" s="54">
+      <c r="A24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="69" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>チラシ作成自動化</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>マレル全員に展開</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>自走率 30% 目標</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Q4 計画 + Flywheel MVP ロードマップ</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2772,952 +2780,989 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.83203125" defaultRowHeight="20"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="27.33203125" customWidth="1" min="2" max="3"/>
-    <col width="12.6640625" customWidth="1" min="4" max="4"/>
-    <col width="9.1640625" customWidth="1" min="5" max="6"/>
-    <col width="18.1640625" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" style="54" min="1" max="1"/>
+    <col width="27.33203125" customWidth="1" style="54" min="2" max="3"/>
+    <col width="12.6640625" customWidth="1" style="54" min="4" max="4"/>
+    <col width="9.1640625" customWidth="1" style="54" min="5" max="6"/>
+    <col width="18.1640625" customWidth="1" style="54" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="23" customHeight="1" s="54">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>テーマプール — 毎週のテーマ候補</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>週次ロードマップに乗せる前の候補ストック。優先度に応じて週次に組み込む。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="31.5" customHeight="1" s="54">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>テーマ</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>期待アウトプット</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>対象 Surface</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>推定週数</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="54">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>AI 自動化</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>バナー AI 自動化</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>5案/週ペースで作れる状態</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>バナー</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F5" s="37" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Week 3 で着手</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+    <row r="6" ht="24" customHeight="1" s="54">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>AI 自動化</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>チラシ AI 自動化</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>A4 チラシ 7割完成度</t>
         </is>
       </c>
-      <c r="D6" s="38" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>紙</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F6" s="37" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Week 4-6</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+    <row r="7" ht="24" customHeight="1" s="54">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>AI 自動化</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>メール HTML 自動化</t>
         </is>
       </c>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>件名+本文 7割完成度</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>メール</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="40" t="inlineStr">
+      <c r="F7" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G7" s="35" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t>Week 7</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
+    <row r="8" ht="24" customHeight="1" s="54">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>AI 自動化</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Instagram 画像自動化</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>フィード画像 7割完成度</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>SNS 画像</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F8" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Week 16</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+    <row r="9" ht="24" customHeight="1" s="54">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>AI 自動化</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>リール / TikTok 字幕自動化</t>
         </is>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>字幕 7割完成度</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>SNS 動画</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F9" s="41" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G9" s="35" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t>Step 3 以降</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+    <row r="10" ht="24" customHeight="1" s="54">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>AI 自動化</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>YouTube サムネ自動化</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>サムネ 7割完成度</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>SNS 動画</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="41" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Step 3 以降</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="11" ht="24" customHeight="1" s="54">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>AI 自動化</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>提案書 PPT 自動化</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>5枚 PPT 7割完成度</t>
         </is>
       </c>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>提案書</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F11" s="40" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G11" s="35" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t>Step 2 想定</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="42" t="inlineStr">
+    <row r="12" ht="24" customHeight="1" s="54">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>インフラ</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>指示書テンプレ v1 作成</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Standard 形式 Slack 化</t>
         </is>
       </c>
-      <c r="D12" s="38" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>プロセス</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F12" s="37" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="42" t="inlineStr">
+    <row r="13" ht="24" customHeight="1" s="54">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>インフラ</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>brand/fambox/CLAUDE.md v1.0</t>
         </is>
       </c>
-      <c r="C13" s="39" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>全判断基準集約</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>プロセス</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="37" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G13" s="35" t="inlineStr">
+      <c r="G13" s="26" t="inlineStr">
         <is>
           <t>Week 9-11</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="42" t="inlineStr">
+    <row r="14" ht="24" customHeight="1" s="54">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>インフラ</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Surface 別ワークフロー文書化</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>6 Surface 全部完成</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>プロセス</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F14" s="40" t="inlineStr">
+      <c r="F14" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Step 1 後半</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="42" t="inlineStr">
+    <row r="15" ht="24" customHeight="1" s="54">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>インフラ</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>bugs.md 100エントリ到達</t>
         </is>
       </c>
-      <c r="C15" s="39" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>規律集成熟</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>プロセス</t>
         </is>
       </c>
-      <c r="E15" s="36" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>継続</t>
         </is>
       </c>
-      <c r="F15" s="43" t="inlineStr">
+      <c r="F15" s="34" t="inlineStr">
         <is>
           <t>継続</t>
         </is>
       </c>
-      <c r="G15" s="39" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>毎週積み増し</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="42" t="inlineStr">
+    <row r="16" ht="24" customHeight="1" s="54">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>インフラ</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>schema-lint v2 拡張</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Liquid 検証強化</t>
         </is>
       </c>
-      <c r="D16" s="38" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>プロセス</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="40" t="inlineStr">
+      <c r="F16" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>余裕ができたら</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="44" t="inlineStr">
+    <row r="17" ht="24" customHeight="1" s="54">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>学習</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>デザインパターン 3つ追加</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>DS v0.6 化</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F17" s="40" t="inlineStr">
+      <c r="F17" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G17" s="35" t="inlineStr">
+      <c r="G17" s="26" t="inlineStr">
         <is>
           <t>Week 8</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="44" t="inlineStr">
+    <row r="18" ht="24" customHeight="1" s="54">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>学習</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A→B 改良 精度測定</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Learn の定量化</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F18" s="40" t="inlineStr">
+      <c r="F18" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Week 6</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="44" t="inlineStr">
+    <row r="19" ht="24" customHeight="1" s="54">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>学習</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Marc Archeco repo 追読</t>
         </is>
       </c>
-      <c r="C19" s="39" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>取り込み続行</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
       </c>
-      <c r="E19" s="36" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>継続</t>
         </is>
       </c>
-      <c r="F19" s="40" t="inlineStr">
+      <c r="F19" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G19" s="39" t="inlineStr">
+      <c r="G19" s="30" t="inlineStr">
         <is>
           <t>毎週 30分</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="44" t="inlineStr">
+    <row r="20" ht="24" customHeight="1" s="54">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>学習</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Inai さん production 流儀の取込</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>ブランド忠実度学習</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F20" s="40" t="inlineStr">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Step 2 想定</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="45" t="inlineStr">
+    <row r="21" ht="24" customHeight="1" s="54">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>対外</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>6/24 千葉工大講演</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>30分発表 + 録画</t>
         </is>
       </c>
-      <c r="D21" s="36" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>対外</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F21" s="37" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G21" s="35" t="inlineStr">
+      <c r="G21" s="26" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="45" t="inlineStr">
+    <row r="22" ht="24" customHeight="1" s="54">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>対外</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>パンケ活動コンテンツ化</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>講演展開 + ブログ化</t>
         </is>
       </c>
-      <c r="D22" s="38" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>対外</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F22" s="40" t="inlineStr">
+      <c r="F22" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Week 5-6</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="45" t="inlineStr">
+    <row r="23" ht="24" customHeight="1" s="54">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>対外</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Marc チーム会留学</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>1-2回参加</t>
         </is>
       </c>
-      <c r="D23" s="36" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>対外</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F23" s="41" t="inlineStr">
+      <c r="F23" s="32" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G23" s="35" t="inlineStr">
+      <c r="G23" s="26" t="inlineStr">
         <is>
           <t>Week 8 試行</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="45" t="inlineStr">
+    <row r="24" ht="24" customHeight="1" s="54">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>対外</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>AI デザイナーキャリア発信</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Note / Linkedin 記事 1本</t>
         </is>
       </c>
-      <c r="D24" s="38" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>対外</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F24" s="41" t="inlineStr">
+      <c r="F24" s="32" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Step 2 期間</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="46" t="inlineStr">
+    <row r="25" ht="24" customHeight="1" s="54">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>実案件</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>法人ページ全改修</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>LP 完成</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F25" s="37" t="inlineStr">
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G25" s="35" t="inlineStr">
+      <c r="G25" s="26" t="inlineStr">
         <is>
           <t>Week 2-8</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="46" t="inlineStr">
+    <row r="26" ht="24" customHeight="1" s="54">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>実案件</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>お問い合わせページ再構築</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>お問い合わせ最適化</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F26" s="37" t="inlineStr">
+      <c r="F26" s="28" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Week 4-5</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="46" t="inlineStr">
+    <row r="27" ht="24" customHeight="1" s="54">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>実案件</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>導入実績ページ拡張</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>TS Tech 等追加</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F27" s="40" t="inlineStr">
+      <c r="F27" s="31" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G27" s="39" t="inlineStr">
+      <c r="G27" s="30" t="inlineStr">
         <is>
           <t>余裕ができたら</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="46" t="inlineStr">
+    <row r="28" ht="24" customHeight="1" s="54">
+      <c r="A28" s="37" t="inlineStr">
         <is>
           <t>実案件</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>FAMBOX 広告 7割品質達成</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>広告 5案/週 量産</t>
         </is>
       </c>
-      <c r="D28" s="38" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>バナー</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F28" s="37" t="inlineStr">
+      <c r="F28" s="28" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Week 3-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" s="54">
+      <c r="A29" s="73" t="inlineStr">
+        <is>
+          <t>実案件</t>
+        </is>
+      </c>
+      <c r="B29" s="74" t="inlineStr">
+        <is>
+          <t>FAMBOX 梱包用チラシ自動化 (第一弾)</t>
+        </is>
+      </c>
+      <c r="C29" s="75" t="inlineStr">
+        <is>
+          <t>C向け+B向け A4 / 7割品質 1-2時間</t>
+        </is>
+      </c>
+      <c r="D29" s="76" t="inlineStr">
+        <is>
+          <t>紙</t>
+        </is>
+      </c>
+      <c r="E29" s="76" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="F29" s="77" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G29" s="75" t="inlineStr">
+        <is>
+          <t>Week 2 で着手</t>
         </is>
       </c>
     </row>
@@ -3740,215 +3785,215 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.83203125" defaultRowHeight="20"/>
   <cols>
-    <col width="13.6640625" customWidth="1" min="1" max="1"/>
-    <col width="12.6640625" customWidth="1" min="2" max="5"/>
-    <col width="31.83203125" customWidth="1" min="6" max="6"/>
-    <col width="27.33203125" customWidth="1" min="7" max="7"/>
+    <col width="13.6640625" customWidth="1" style="54" min="1" max="1"/>
+    <col width="12.6640625" customWidth="1" style="54" min="2" max="5"/>
+    <col width="31.83203125" customWidth="1" style="54" min="6" max="6"/>
+    <col width="27.33203125" customWidth="1" style="54" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="23" customHeight="1" s="54">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>月次レビュー — 達成率と計画修正</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>毎月最終週の月曜投稿に月次サマリを兼ねる。3週連続で達成率 50% 未満 → 緊急ルール発動。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="31.5" customHeight="1" s="54">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>完了 Week 数</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>達成宣言数</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>総宣言数</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>達成率%</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>主な学び</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>計画修正</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="39.75" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
+    <row r="5" ht="39.75" customHeight="1" s="54">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n">
+      <c r="B5" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="n">
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="E5" s="48" t="n"/>
-      <c r="F5" s="39" t="n"/>
-      <c r="G5" s="39" t="n"/>
-    </row>
-    <row r="6" ht="39.75" customHeight="1">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="E5" s="39" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="39.75" customHeight="1" s="54">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n">
+      <c r="B6" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="38" t="n"/>
-      <c r="D6" s="38" t="n">
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="E6" s="50" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-    </row>
-    <row r="7" ht="39.75" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="E6" s="41" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="39.75" customHeight="1" s="54">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n">
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="E7" s="48" t="n"/>
-      <c r="F7" s="39" t="n"/>
-      <c r="G7" s="39" t="n"/>
-    </row>
-    <row r="8" ht="39.75" customHeight="1">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="39.75" customHeight="1" s="54">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B8" s="38" t="n">
+      <c r="B8" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="38" t="n"/>
-      <c r="D8" s="38" t="n">
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="E8" s="50" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-    </row>
-    <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="E8" s="41" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="39.75" customHeight="1" s="54">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n">
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="E9" s="48" t="n"/>
-      <c r="F9" s="39" t="n"/>
-      <c r="G9" s="39" t="n"/>
-    </row>
-    <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+    </row>
+    <row r="10" ht="39.75" customHeight="1" s="54">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n">
+      <c r="B10" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="38" t="n">
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="E10" s="50" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="47" t="inlineStr">
+      <c r="E10" s="41" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="39.75" customHeight="1" s="54">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n">
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="E11" s="48" t="n"/>
-      <c r="F11" s="39" t="n"/>
-      <c r="G11" s="39" t="n"/>
-    </row>
-    <row r="12" ht="39.75" customHeight="1">
-      <c r="A12" s="49" t="inlineStr">
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+    </row>
+    <row r="12" ht="39.75" customHeight="1" s="54">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="B12" s="38" t="n"/>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="50" t="n"/>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Step 3 開始判定</t>
         </is>
       </c>
-      <c r="G12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="39.75" customHeight="1">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="39.75" customHeight="1" s="54">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>2027-Q1 末</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="48" t="n"/>
-      <c r="F13" s="35" t="inlineStr">
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="26" t="inlineStr">
         <is>
           <t>Flywheel MVP 完成判定</t>
         </is>
       </c>
-      <c r="G13" s="39" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
